--- a/ejemplo/visitas-ejemplo.xlsx
+++ b/ejemplo/visitas-ejemplo.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,26 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000B1F33"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,10 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,51 +413,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>LISTADO DE VISITAS — EJEMPLO</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Folio</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Domicilio</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Colonia / Fracc. / Poblado</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Teléfono</t>
         </is>
@@ -481,22 +458,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VIS-1054</t>
+          <t>VIS-1095</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Castro Castro María</t>
+          <t>Flores Flores Guadalupe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pino Suárez 1147</t>
+          <t>Juárez 1297</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>Tierra y Libertad</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -506,29 +483,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6188687243</t>
+          <t>6185332955</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VIS-1031</t>
+          <t>VIS-1138</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Castro Castro Rosa</t>
+          <t>Flores Flores Juan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Juárez 209</t>
+          <t>Pino Suárez 283</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Las Alamedas</t>
+          <t>Navacoyán</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -538,29 +515,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6183716256</t>
+          <t>6185722030</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VIS-1063</t>
+          <t>VIS-1024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Castro Flores Miguel</t>
+          <t>Flores García Luis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20 de Noviembre 448</t>
+          <t>Hidalgo 312</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Col. Morelos Norte</t>
+          <t>FRACC. VALLE DEL SUR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -570,29 +547,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6182038860</t>
+          <t>6181649219</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VIS-1044</t>
+          <t>VIS-1111</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Castro González Carlos</t>
+          <t>Flores Hernández Jorge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Felipe Pescador 1322</t>
+          <t>Pino Suárez 937</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gobernadores</t>
+          <t>El Pueblito</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -602,29 +579,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6186704991</t>
+          <t>6181885693</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VIS-1035</t>
+          <t>VIS-1037</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Castro Pérez Patricia</t>
+          <t>Flores Hernández Patricia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Constitución 578</t>
+          <t>Zaragoza 264</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Labor de Guadalupe</t>
+          <t>Nueva Vizcaya</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -634,29 +611,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6187711858</t>
+          <t>6182939116</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VIS-1067</t>
+          <t>VIS-1079</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Castro Reyes Ana</t>
+          <t>Flores Martínez Carlos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 1186</t>
+          <t>Negrete 1869</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Las Alamedas</t>
+          <t>Guillermina</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -666,29 +643,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6182797887</t>
+          <t>6184663200</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VIS-1047</t>
+          <t>VIS-1101</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Castro Rodríguez Jorge</t>
+          <t>Flores Martínez Carlos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Coronado 861</t>
+          <t>Zaragoza 897</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fracc. Fidel Velázquez II</t>
+          <t>El Arenal</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -698,29 +675,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6183929684</t>
+          <t>6189348258</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VIS-1004</t>
+          <t>VIS-1030</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Flores Flores Laura</t>
+          <t>Flores Martínez José</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zaragoza 1830</t>
+          <t>20 de Noviembre 383</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Benito Juárez</t>
+          <t>Villa Montemorelos</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -730,29 +707,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6187508416</t>
+          <t>6186552670</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VIS-1077</t>
+          <t>VIS-1137</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Flores Flores Luis</t>
+          <t>Flores Pérez Guadalupe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aquiles Serdán 1540</t>
+          <t>Victoria 854</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo</t>
+          <t>El Pueblito</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -762,29 +739,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6186399662</t>
+          <t>6183596887</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VIS-1048</t>
+          <t>VIS-1065</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Flores Hernández María</t>
+          <t>Flores Soto José</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Juárez 1645</t>
+          <t>Negrete 999</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nueva Vizcaya</t>
+          <t>Ciudad Industrial</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -794,29 +771,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6187023345</t>
+          <t>6185868239</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VIS-1073</t>
+          <t>VIS-1088</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Flores López María</t>
+          <t>Flores Sánchez Juan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zaragoza 1828</t>
+          <t>Negrete 477</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Silvestre Revueltas</t>
+          <t>Huizache I</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -826,29 +803,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6185600661</t>
+          <t>6184421109</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VIS-1015</t>
+          <t>VIS-1021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Flores Pérez Ricardo</t>
+          <t>Flores Sánchez Patricia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5 de Febrero 379</t>
+          <t>Pino Suárez 1874</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>José Revueltas</t>
+          <t>El Pueblito</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -858,29 +835,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6187402766</t>
+          <t>6184067340</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VIS-1008</t>
+          <t>VIS-1011</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Flores Ramírez José</t>
+          <t>García Flores Jorge</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Zaragoza 194</t>
+          <t>Negrete 1694</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Villa Montemorelos</t>
+          <t>Ciénega</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -890,29 +867,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6185704888</t>
+          <t>6186652123</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VIS-1117</t>
+          <t>VIS-1103</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Flores Reyes Luis</t>
+          <t>García Flores José</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Juárez 1091</t>
+          <t>Negrete 625</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lucio Cabañas</t>
+          <t>Villa Montemorelos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -922,29 +899,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6185514352</t>
+          <t>6187736985</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VIS-1114</t>
+          <t>VIS-1124</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Flores Soto Francisco</t>
+          <t>García García Jorge</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Juárez 842</t>
+          <t>Pino Suárez 1227</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Villa Montemorelos</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -954,29 +931,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>6185153656</t>
+          <t>6187260981</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>VIS-1100</t>
+          <t>VIS-1012</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Flores Sánchez Verónica</t>
+          <t>García González Ana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aquiles Serdán 743</t>
+          <t>Hidalgo 939</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Gobernadores</t>
+          <t>Huizache I</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -986,29 +963,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6183853790</t>
+          <t>6183258154</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VIS-1094</t>
+          <t>VIS-1142</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>García Flores Miguel</t>
+          <t>García Hernández Jorge</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pino Suárez 385</t>
+          <t>Pino Suárez 299</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Col. Morelos Norte</t>
+          <t>Cinco de Mayo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1018,29 +995,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6188780390</t>
+          <t>6185117971</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VIS-1023</t>
+          <t>VIS-1063</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>García García Carlos</t>
+          <t>García Pérez María</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5 de Febrero 596</t>
+          <t>Pino Suárez 1191</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>El Arenal</t>
+          <t>Tierra y Libertad</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1050,29 +1027,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6184490759</t>
+          <t>6183357202</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VIS-1057</t>
+          <t>VIS-1130</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>García Rodríguez Miguel</t>
+          <t>García Ramírez José</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Felipe Pescador 1291</t>
+          <t>Constitución 1255</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>José Revueltas</t>
+          <t>Fracc Las Fuentes</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1082,29 +1059,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6181310836</t>
+          <t>6189134548</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VIS-1029</t>
+          <t>VIS-1094</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>García Rodríguez Ricardo</t>
+          <t>García Ramírez María</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Victoria 1067</t>
+          <t>20 de Noviembre 1929</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>El Pueblito</t>
+          <t>Nueva Vizcaya</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1114,29 +1091,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>6187550534</t>
+          <t>6187786550</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VIS-1076</t>
+          <t>VIS-1034</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>García Rodríguez Verónica</t>
+          <t>García Sánchez Carlos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bruno Martínez 230</t>
+          <t>20 de Noviembre 1609</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Morcillo</t>
+          <t>Fracc. Huizache 2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1146,29 +1123,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6189538403</t>
+          <t>6183173395</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VIS-1013</t>
+          <t>VIS-1040</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>García Soto Juan</t>
+          <t>González Flores José</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5 de Febrero 1605</t>
+          <t>Bruno Martínez 145</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fracc. Fidel Velázquez II</t>
+          <t>Silvestre Revueltas</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1178,29 +1155,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6181305136</t>
+          <t>6182893894</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VIS-1019</t>
+          <t>VIS-1096</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>González García Claudia</t>
+          <t>González García Laura</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Victoria 610</t>
+          <t>Pino Suárez 1768</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fracc. Fidel Velázquez II</t>
+          <t>Ejido Contreras</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1210,29 +1187,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6181596831</t>
+          <t>6183234977</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VIS-1045</t>
+          <t>VIS-1105</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>González Ortiz Juan</t>
+          <t>González González Ana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Victoria 394</t>
+          <t>Juárez 1206</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Domingo Arrieta</t>
+          <t>El Arenal</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1242,29 +1219,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6185787651</t>
+          <t>6187974074</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VIS-1090</t>
+          <t>VIS-1120</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>González Soto Rosa</t>
+          <t>González González Patricia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5 de Febrero 587</t>
+          <t>Victoria 1531</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gobernadores</t>
+          <t>Amp. PRI</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1274,29 +1251,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>6184263818</t>
+          <t>6184188084</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VIS-1034</t>
+          <t>VIS-1042</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hernández Flores Laura</t>
+          <t>González Martínez Jorge</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 253</t>
+          <t>Victoria 514</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nueva Vizcaya</t>
+          <t>Ciudad Industrial</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1306,29 +1283,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6188612993</t>
+          <t>6183845535</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VIS-1006</t>
+          <t>VIS-1047</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hernández Flores Patricia</t>
+          <t>González Martínez José</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 1667</t>
+          <t>Bruno Martínez 1065</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Morcillo</t>
+          <t>Ciénega</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1338,29 +1315,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6184273657</t>
+          <t>6184591672</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VIS-1074</t>
+          <t>VIS-1019</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hernández García María</t>
+          <t>González Pérez José</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bruno Martínez 1528</t>
+          <t>Zaragoza 284</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>El Ciprés</t>
+          <t>Insurgentes</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1370,29 +1347,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6184575934</t>
+          <t>6185077080</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VIS-1096</t>
+          <t>VIS-1038</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hernández Ortiz Luis</t>
+          <t>González Pérez Laura</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Zaragoza 776</t>
+          <t>20 de Noviembre 895</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Lucio Cabañas</t>
+          <t>Amp. PRI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1402,29 +1379,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>6181911694</t>
+          <t>6188679867</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VIS-1040</t>
+          <t>VIS-1026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hernández Rodríguez María</t>
+          <t>González Ramírez Juan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Coronado 738</t>
+          <t>Zaragoza 358</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Huizache I</t>
+          <t>Silvestre Revueltas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1434,29 +1411,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6182859564</t>
+          <t>6189041318</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VIS-1107</t>
+          <t>VIS-1067</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hernández Soto Laura</t>
+          <t>González Reyes Luis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zaragoza 510</t>
+          <t>Victoria 526</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo</t>
+          <t>Villas del Guadiana</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1466,29 +1443,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>6182342858</t>
+          <t>6183368109</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VIS-1025</t>
+          <t>VIS-1020</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>López Castro José</t>
+          <t>Hernández Flores Ana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bruno Martínez 893</t>
+          <t>20 de Noviembre 1374</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Nueva Vizcaya</t>
+          <t>Navacoyán</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1498,29 +1475,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6188216007</t>
+          <t>6183134415</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VIS-1020</t>
+          <t>VIS-1115</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>López Flores Verónica</t>
+          <t>Hernández Flores Luis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Coronado 510</t>
+          <t>Bruno Martínez 341</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Navacoyán</t>
+          <t>Insurgentes</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1530,29 +1507,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>6184385184</t>
+          <t>6181873349</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VIS-1036</t>
+          <t>VIS-1139</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>López Martínez Guadalupe</t>
+          <t>Hernández López Carlos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Victoria 1735</t>
+          <t>Hidalgo 1214</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Gobernadores</t>
+          <t>Real del Prado</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1562,29 +1539,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>6189597897</t>
+          <t>6185964028</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VIS-1093</t>
+          <t>VIS-1092</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>López Pérez Patricia</t>
+          <t>Hernández Reyes Laura</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 1513</t>
+          <t>Hidalgo 1829</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fracc. Fidel Velázquez II</t>
+          <t>Las Alamedas II</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1594,29 +1571,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6189343829</t>
+          <t>6184041192</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VIS-1059</t>
+          <t>VIS-1140</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>López Ramírez José</t>
+          <t>Hernández Reyes Luis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Coronado 691</t>
+          <t>Zaragoza 1291</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Domingo Arrieta</t>
+          <t>Guillermina</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1626,29 +1603,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>6183503111</t>
+          <t>6186125014</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VIS-1112</t>
+          <t>VIS-1032</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>López Reyes Jorge</t>
+          <t>Hernández Sánchez Ana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Coronado 667</t>
+          <t>5 de Febrero 168</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fidel Velázquez</t>
+          <t>Col. Jardines de Durango</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1658,29 +1635,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>6182982908</t>
+          <t>6182255500</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VIS-1049</t>
+          <t>VIS-1036</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>López Rodríguez Ana</t>
+          <t>Hernández Sánchez Patricia</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Victoria 1114</t>
+          <t>Hidalgo 1379</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>El Pueblito</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1690,29 +1667,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>6182959987</t>
+          <t>6187361524</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>VIS-1062</t>
+          <t>VIS-1085</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Martínez Castro Ana</t>
+          <t>López Flores Jorge</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pino Suárez 1891</t>
+          <t>20 de Noviembre 1966</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>José Revueltas</t>
+          <t>Col. Morelos Norte</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1722,29 +1699,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>6189637527</t>
+          <t>6182936262</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VIS-1113</t>
+          <t>VIS-1136</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Martínez Hernández Ana</t>
+          <t>López García Ana</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hidalgo 1672</t>
+          <t>20 de Noviembre 149</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ciénega</t>
+          <t>Col. Morelos Norte</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1754,29 +1731,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>6188129066</t>
+          <t>6187637227</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VIS-1001</t>
+          <t>VIS-1100</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Martínez Martínez María</t>
+          <t>López González Jorge</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Constitución 1225</t>
+          <t>5 de Febrero 791</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lucio Cabañas</t>
+          <t>Insurgentes</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1786,29 +1763,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>6181987289</t>
+          <t>6187813752</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VIS-1097</t>
+          <t>VIS-1016</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Martínez Quiñones Ana</t>
+          <t>López Hernández Francisco</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Coronado 1179</t>
+          <t>Victoria 722</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Hipódromo</t>
+          <t>Col. Jardines de Durango</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1818,29 +1795,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>6184038379</t>
+          <t>6184535130</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VIS-1028</t>
+          <t>VIS-1029</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Martínez Ramírez Luis</t>
+          <t>López Hernández María</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hidalgo 908</t>
+          <t>Pino Suárez 677</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fidel Velázquez</t>
+          <t>Col. Morelos Norte</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1850,29 +1827,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>6185520479</t>
+          <t>6189908762</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VIS-1065</t>
+          <t>VIS-1082</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Martínez Rodríguez Guadalupe</t>
+          <t>López López Guadalupe</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 1347</t>
+          <t>Zaragoza 374</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Zona Centro</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1882,29 +1859,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>6184892619</t>
+          <t>6183223678</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VIS-1070</t>
+          <t>VIS-1010</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Martínez Sánchez Jorge</t>
+          <t>López López María</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Zaragoza 1448</t>
+          <t>Bruno Martínez 868</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Guadalupe</t>
+          <t>Ejido Contreras</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1914,29 +1891,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>6186408113</t>
+          <t>6188042931</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VIS-1108</t>
+          <t>VIS-1075</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ortiz García Patricia</t>
+          <t>López Martínez Guadalupe</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Negrete 1832</t>
+          <t>Hidalgo 1507</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Las Alamedas</t>
+          <t>Lucio Cabañas</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1946,29 +1923,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>6183884905</t>
+          <t>6186403643</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VIS-1060</t>
+          <t>VIS-1052</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ortiz González Juan</t>
+          <t>López Martínez María</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Juárez 846</t>
+          <t>Zaragoza 1014</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Zona Centro</t>
+          <t>FRACC. VALLE DEL SUR</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1978,29 +1955,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>6183613578</t>
+          <t>6189982380</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>VIS-1061</t>
+          <t>VIS-1045</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ortiz González Luis</t>
+          <t>López Pérez Guadalupe</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 710</t>
+          <t>Victoria 1985</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Navacoyán</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2010,29 +1987,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>6189516004</t>
+          <t>6184521412</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VIS-1053</t>
+          <t>VIS-1060</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ortiz Hernández Carlos</t>
+          <t>López Pérez José</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pino Suárez 1937</t>
+          <t>5 de Febrero 1199</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Villa Montemorelos</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2042,29 +2019,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>6187111968</t>
+          <t>6185393670</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VIS-1064</t>
+          <t>VIS-1113</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ortiz Hernández Carlos</t>
+          <t>López Pérez Laura</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Coronado 138</t>
+          <t>Bruno Martínez 613</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Villas del Guadiana</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2074,29 +2051,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>6183558745</t>
+          <t>6181762255</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VIS-1110</t>
+          <t>VIS-1149</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ortiz Martínez Juan</t>
+          <t>López Pérez Luis</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Juárez 1411</t>
+          <t>Juárez 698</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Benito Juárez</t>
+          <t>Ciénega</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2106,29 +2083,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>6183827368</t>
+          <t>6181993328</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VIS-1007</t>
+          <t>VIS-1006</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ortiz Ortiz Patricia</t>
+          <t>López Reyes Francisco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Constitución 1024</t>
+          <t>Bruno Martínez 109</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Real del Prado</t>
+          <t>Nueva Vizcaya</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2138,29 +2115,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>6184912869</t>
+          <t>6188672722</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VIS-1037</t>
+          <t>VIS-1013</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ortiz Ortiz Ricardo</t>
+          <t>López Soto José</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Zaragoza 1387</t>
+          <t>Hidalgo 222</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Las Alamedas</t>
+          <t>Navacoyán</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2170,29 +2147,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>6186071844</t>
+          <t>6189167539</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VIS-1027</t>
+          <t>VIS-1148</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ortiz Pérez Carlos</t>
+          <t>López Soto Juan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>20 de Noviembre 1989</t>
+          <t>Constitución 1500</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>El Pueblito</t>
+          <t>Real del Prado</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2202,29 +2179,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>6189328049</t>
+          <t>6186383466</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VIS-1018</t>
+          <t>VIS-1028</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ortiz Pérez Guadalupe</t>
+          <t>López Soto María</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hidalgo 227</t>
+          <t>Zaragoza 651</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Hipódromo</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2234,29 +2211,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>6183829817</t>
+          <t>6188477697</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VIS-1099</t>
+          <t>VIS-1018</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ortiz Sánchez Francisco</t>
+          <t>López Sánchez Francisco</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Victoria 187</t>
+          <t>Hidalgo 1682</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fidel Velázquez</t>
+          <t>Colonia Inventada XYZ</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2266,29 +2243,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>6184069577</t>
+          <t>6186518956</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VIS-1111</t>
+          <t>VIS-1133</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pérez García José</t>
+          <t>Martínez López Ana</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Zaragoza 385</t>
+          <t>20 de Noviembre 850</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo</t>
+          <t>Huizache I</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2298,29 +2275,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>6183273237</t>
+          <t>6186409732</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VIS-1088</t>
+          <t>VIS-1089</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pérez González Miguel</t>
+          <t>Martínez Martínez Francisco</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bruno Martínez 1331</t>
+          <t>Zaragoza 1287</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Labor de Guadalupe</t>
+          <t>Hipódromo</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2330,29 +2307,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>6186430972</t>
+          <t>6183255701</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>VIS-1003</t>
+          <t>VIS-1046</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pérez Hernández Carlos</t>
+          <t>Martínez Martínez Rosa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Felipe Pescador 656</t>
+          <t>20 de Noviembre 1814</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Las Alamedas</t>
+          <t>Fracc. Huizache 2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2362,29 +2339,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>6183765191</t>
+          <t>6182076074</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VIS-1030</t>
+          <t>VIS-1017</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pérez Hernández Luis</t>
+          <t>Martínez Pérez Patricia</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pino Suárez 126</t>
+          <t>Victoria 305</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>José Revueltas</t>
+          <t>Fracc. Huizache 2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2394,29 +2371,29 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>6182944311</t>
+          <t>6183455489</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>VIS-1109</t>
+          <t>VIS-1001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pérez Martínez Juan</t>
+          <t>Martínez Ramírez Rosa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hidalgo 1919</t>
+          <t>Victoria 1724</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Zona Centro</t>
+          <t>Domingo Arrieta</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2426,29 +2403,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>6185889504</t>
+          <t>6182579129</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VIS-1082</t>
+          <t>VIS-1014</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pérez Quiñones Guadalupe</t>
+          <t>Martínez Reyes Carlos</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Coronado 797</t>
+          <t>Negrete 1016</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Zona Centro</t>
+          <t>El Arenal</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2458,29 +2435,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>6188644129</t>
+          <t>6184199153</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VIS-1069</t>
+          <t>VIS-1128</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pérez Ramírez Patricia</t>
+          <t>Martínez Reyes Patricia</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Felipe Pescador 1934</t>
+          <t>20 de Noviembre 695</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Navacoyán</t>
+          <t>Colonia José Ángel Leal</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2490,29 +2467,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>6186689937</t>
+          <t>6184084782</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VIS-1011</t>
+          <t>VIS-1074</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pérez Reyes Guadalupe</t>
+          <t>Pérez Flores María</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 226</t>
+          <t>5 de Febrero 365</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Silvestre Revueltas</t>
+          <t>Col. Jardines de Durango</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2522,29 +2499,29 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>6185655321</t>
+          <t>6181597685</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VIS-1103</t>
+          <t>VIS-1009</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pérez Rodríguez Francisco</t>
+          <t>Pérez García Francisco</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Juárez 1556</t>
+          <t>Constitución 236</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fidel Velázquez</t>
+          <t>Col. Jardines de Durango</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2554,29 +2531,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>6181862947</t>
+          <t>6181009142</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VIS-1026</t>
+          <t>VIS-1146</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pérez Rodríguez Jorge</t>
+          <t>Pérez García Rosa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>5 de Febrero 1445</t>
+          <t>Juárez 1411</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Navacoyán</t>
+          <t>Col. Jardines de Durango</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2586,29 +2563,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>6186285446</t>
+          <t>6189788847</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VIS-1083</t>
+          <t>VIS-1123</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pérez Rodríguez Juan</t>
+          <t>Pérez Hernández Patricia</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Negrete 1163</t>
+          <t>Hidalgo 309</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fracc. Valle del Sur</t>
+          <t>Silvestre Revueltas</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2618,29 +2595,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>6182912670</t>
+          <t>6185668904</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VIS-1119</t>
+          <t>VIS-1098</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pérez Rodríguez Ricardo</t>
+          <t>Pérez López Laura</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Zaragoza 735</t>
+          <t>Pino Suárez 244</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Guadalupe</t>
+          <t>Tierra y Libertad</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2650,29 +2627,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>6189742631</t>
+          <t>6186061508</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VIS-1092</t>
+          <t>VIS-1107</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pérez Soto Ana</t>
+          <t>Pérez Martínez Luis</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Juárez 535</t>
+          <t>Bruno Martínez 446</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Jardines de Durango</t>
+          <t>Morcillo</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2682,29 +2659,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>6181452231</t>
+          <t>6181982227</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VIS-1010</t>
+          <t>VIS-1072</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pérez Valles Carlos</t>
+          <t>Pérez Pérez Francisco</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pino Suárez 828</t>
+          <t>Negrete 1069</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo</t>
+          <t>Morcillo</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2714,29 +2691,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>6186379931</t>
+          <t>6183130162</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VIS-1106</t>
+          <t>VIS-1048</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Quiñones Flores José</t>
+          <t>Pérez Pérez Jorge</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pino Suárez 689</t>
+          <t>Juárez 1111</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Contreras</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2746,29 +2723,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>6181754873</t>
+          <t>6188591310</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VIS-1056</t>
+          <t>VIS-1091</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Quiñones Martínez Francisco</t>
+          <t>Pérez Ramírez Ana</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Negrete 241</t>
+          <t>Constitución 530</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Villas del Guadiana</t>
+          <t>Esperanza</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2778,29 +2755,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>6183225374</t>
+          <t>6187260484</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VIS-1038</t>
+          <t>VIS-1129</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Quiñones Ortiz Guadalupe</t>
+          <t>Pérez Reyes Ana</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Felipe Pescador 1243</t>
+          <t>Victoria 298</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Real del Prado</t>
+          <t>Navacoyán</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2810,29 +2787,29 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>6187234462</t>
+          <t>6186438394</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VIS-1041</t>
+          <t>VIS-1044</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Quiñones Quiñones Juan</t>
+          <t>Pérez Reyes Francisco</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Juárez 602</t>
+          <t>Negrete 1398</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Contreras</t>
+          <t>Cinco de Mayo</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2842,29 +2819,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>6185923290</t>
+          <t>6184360340</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VIS-1033</t>
+          <t>VIS-1057</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Quiñones Ramírez Francisco</t>
+          <t>Pérez Soto Luis</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hidalgo 842</t>
+          <t>Pino Suárez 1022</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Nueva Vizcaya</t>
+          <t>Navacoyán</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2874,29 +2851,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>6189774253</t>
+          <t>6184303043</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VIS-1009</t>
+          <t>VIS-1093</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Quiñones Reyes Francisco</t>
+          <t>Pérez Sánchez Ana</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Coronado 500</t>
+          <t>20 de Noviembre 930</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>Las Alamedas II</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2906,29 +2883,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>6187925545</t>
+          <t>6183769526</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VIS-1071</t>
+          <t>VIS-1108</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Quiñones Soto Juan</t>
+          <t>Pérez Sánchez Luis</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pino Suárez 1561</t>
+          <t>5 de Febrero 1178</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Guadalupe</t>
+          <t>Ejido Contreras</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2938,29 +2915,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>6189356488</t>
+          <t>6186241110</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VIS-1068</t>
+          <t>VIS-1106</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Quiñones Soto Patricia</t>
+          <t>Ramírez Flores José</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Coronado 1803</t>
+          <t>Bruno Martínez 1757</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Contreras</t>
+          <t>LOS ANGELES</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2970,29 +2947,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>6181624545</t>
+          <t>6181756880</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VIS-1105</t>
+          <t>VIS-1056</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ramírez García Patricia</t>
+          <t>Ramírez Flores Juan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bruno Martínez 1907</t>
+          <t>Constitución 1838</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ciénega</t>
+          <t>Silvestre Revueltas</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3002,29 +2979,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>6184508242</t>
+          <t>6182463135</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VIS-1080</t>
+          <t>VIS-1141</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ramírez Martínez María</t>
+          <t>Ramírez García Ana</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Constitución 639</t>
+          <t>Zaragoza 660</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Lucio Cabañas</t>
+          <t>FRACC. VALLE DEL SUR</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3034,29 +3011,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>6183221329</t>
+          <t>6186264810</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VIS-1116</t>
+          <t>VIS-1069</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ramírez Valles Jorge</t>
+          <t>Ramírez García Carlos</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pino Suárez 722</t>
+          <t>Hidalgo 1339</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Real del Prado</t>
+          <t>El Pueblito</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3066,29 +3043,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>6186306137</t>
+          <t>6181465660</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VIS-1084</t>
+          <t>VIS-1114</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Reyes Flores Francisco</t>
+          <t>Ramírez García Laura</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Aquiles Serdán 255</t>
+          <t>Bruno Martínez 395</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Domingo Arrieta</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3098,29 +3075,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>6181456672</t>
+          <t>6182930944</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VIS-1014</t>
+          <t>VIS-1004</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Reyes Flores Jorge</t>
+          <t>Ramírez García María</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pino Suárez 1687</t>
+          <t>Hidalgo 489</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Contreras</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3130,29 +3107,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>6182304534</t>
+          <t>6181504702</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VIS-1081</t>
+          <t>VIS-1025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Reyes Martínez Ana</t>
+          <t>Ramírez González Guadalupe</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Victoria 288</t>
+          <t>Constitución 626</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Insurgentes</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3162,29 +3139,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>6185254709</t>
+          <t>6189237604</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VIS-1079</t>
+          <t>VIS-1135</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Reyes Ortiz Verónica</t>
+          <t>Ramírez González Rosa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>20 de Noviembre 1636</t>
+          <t>20 de Noviembre 553</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Insurgentes</t>
+          <t>Ejido Contreras</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3194,29 +3171,29 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>6185294769</t>
+          <t>6189659828</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VIS-1032</t>
+          <t>VIS-1070</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Reyes Quiñones Ricardo</t>
+          <t>Ramírez Hernández Carlos</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hidalgo 261</t>
+          <t>Constitución 1214</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Guadalupe</t>
+          <t>Fracc Las Fuentes</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3226,29 +3203,29 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>6182894424</t>
+          <t>6183045661</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VIS-1043</t>
+          <t>VIS-1104</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Reyes Valles Patricia</t>
+          <t>Ramírez Hernández Guadalupe</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 1137</t>
+          <t>Constitución 122</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cinco de Mayo</t>
+          <t>FRACC. VALLE DEL SUR</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3258,29 +3235,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>6188416628</t>
+          <t>6185337876</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VIS-1087</t>
+          <t>VIS-1080</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rodríguez García Carlos</t>
+          <t>Ramírez López Carlos</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Aquiles Serdán 1986</t>
+          <t>Victoria 1301</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Labor de Guadalupe</t>
+          <t>Fidel Velázquez</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3290,29 +3267,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>6182748823</t>
+          <t>6184903360</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VIS-1085</t>
+          <t>VIS-1068</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Rodríguez Pérez Carlos</t>
+          <t>Ramírez Ramírez Francisco</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hidalgo 1315</t>
+          <t>Victoria 1119</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fracc. Fidel Velázquez II</t>
+          <t>Las Alamedas II</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3322,29 +3299,29 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>6186505287</t>
+          <t>6187896837</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VIS-1078</t>
+          <t>VIS-1027</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rodríguez Pérez María</t>
+          <t>Ramírez Reyes Patricia</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bruno Martínez 1916</t>
+          <t>Victoria 251</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo</t>
+          <t>Ciénega</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3354,29 +3331,29 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>6185629590</t>
+          <t>6184563484</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VIS-1050</t>
+          <t>VIS-1084</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Rodríguez Quiñones Rosa</t>
+          <t>Ramírez Soto Juan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Victoria 1711</t>
+          <t>Negrete 924</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Villas del Guadiana</t>
+          <t>Col. Jardines de Durango</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3386,29 +3363,29 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>6187813418</t>
+          <t>6182611566</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VIS-1016</t>
+          <t>VIS-1132</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Rodríguez Reyes María</t>
+          <t>Reyes Flores José</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>20 de Noviembre 191</t>
+          <t>5 de Febrero 1113</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Villa Montemorelos</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3418,29 +3395,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>6183844862</t>
+          <t>6185746529</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VIS-1039</t>
+          <t>VIS-1121</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Rodríguez Rodríguez Francisco</t>
+          <t>Reyes González Guadalupe</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>20 de Noviembre 1112</t>
+          <t>Negrete 609</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Benito Juárez</t>
+          <t>El Arenal</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3450,29 +3427,29 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>6185338773</t>
+          <t>6184287961</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VIS-1091</t>
+          <t>VIS-1007</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Soto Castro Laura</t>
+          <t>Reyes González Luis</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Juárez 1550</t>
+          <t>Juárez 1820</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Huizache I</t>
+          <t>Nueva Vizcaya</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3482,29 +3459,29 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>6184766605</t>
+          <t>6185261324</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VIS-1055</t>
+          <t>VIS-1122</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Soto Flores Juan</t>
+          <t>Reyes Hernández Jorge</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Felipe Pescador 628</t>
+          <t>Hidalgo 119</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Navacoyán</t>
+          <t>Ciénega</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3514,29 +3491,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>6184727252</t>
+          <t>6185354004</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VIS-1104</t>
+          <t>VIS-1058</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Soto Martínez José</t>
+          <t>Reyes Hernández Luis</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Felipe Pescador 1813</t>
+          <t>Juárez 1264</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>El Ciprés</t>
+          <t>El Arenal</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3546,29 +3523,29 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>6183953137</t>
+          <t>6186756222</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VIS-1089</t>
+          <t>VIS-1102</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Soto Ortiz Miguel</t>
+          <t>Reyes López Laura</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 174</t>
+          <t>Zaragoza 1660</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Guadalupe</t>
+          <t>Ejido Contreras</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3578,29 +3555,29 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>6184040556</t>
+          <t>6181382864</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VIS-1102</t>
+          <t>VIS-1022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Soto Pérez Claudia</t>
+          <t>Reyes Martínez Francisco</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bruno Martínez 1797</t>
+          <t>Negrete 1774</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Huizache I</t>
+          <t>Colonia Inventada XYZ</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3610,29 +3587,29 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>6182240466</t>
+          <t>6185185891</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VIS-1046</t>
+          <t>VIS-1051</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Soto Pérez Laura</t>
+          <t>Reyes Martínez Luis</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Coronado 1371</t>
+          <t>Bruno Martínez 488</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Nueva Vizcaya</t>
+          <t>Col. Jardines de Durango</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3642,29 +3619,29 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>6182292873</t>
+          <t>6185469660</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>VIS-1086</t>
+          <t>VIS-1117</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Soto Rodríguez Ana</t>
+          <t>Reyes Pérez Rosa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Felipe Pescador 540</t>
+          <t>Victoria 636</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Hipódromo</t>
+          <t>Amp. PRI</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3674,29 +3651,29 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>6181896739</t>
+          <t>6188038575</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VIS-1118</t>
+          <t>VIS-1053</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Soto Rodríguez Jorge</t>
+          <t>Reyes Reyes Ana</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Zaragoza 1868</t>
+          <t>Zaragoza 1501</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Silvestre Revueltas</t>
+          <t>Las Alamedas II</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3706,29 +3683,29 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>6186511635</t>
+          <t>6184344394</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VIS-1101</t>
+          <t>VIS-1050</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Soto Soto Carlos</t>
+          <t>Reyes Soto Francisco</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Victoria 786</t>
+          <t>Victoria 825</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Guadalupe</t>
+          <t>Villas del Guadiana</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3738,24 +3715,24 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>6183552269</t>
+          <t>6181320679</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VIS-1095</t>
+          <t>VIS-1031</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Soto Soto María</t>
+          <t>Reyes Soto Laura</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bruno Martínez 1529</t>
+          <t>Juárez 1296</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3770,29 +3747,29 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>6188506824</t>
+          <t>6181588553</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>VIS-1017</t>
+          <t>VIS-1110</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Soto Soto Patricia</t>
+          <t>Reyes Soto Laura</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Victoria 298</t>
+          <t>5 de Febrero 155</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cinco de Mayo</t>
+          <t>Zona Centro</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3802,29 +3779,29 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>6184476855</t>
+          <t>6185110800</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VIS-1042</t>
+          <t>VIS-1131</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Soto Sánchez Ana</t>
+          <t>Reyes Sánchez Francisco</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 1383</t>
+          <t>Hidalgo 255</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Zona Centro</t>
+          <t>Villas del Guadiana</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3834,29 +3811,29 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>6181887840</t>
+          <t>6184577915</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>VIS-1075</t>
+          <t>VIS-1090</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Soto Sánchez Laura</t>
+          <t>Reyes Sánchez José</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 710</t>
+          <t>Zaragoza 769</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Col. Morelos Norte</t>
+          <t>Ejido Contreras</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3866,29 +3843,29 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>6187754965</t>
+          <t>6188834286</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VIS-1000</t>
+          <t>VIS-1049</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sánchez Flores Guadalupe</t>
+          <t>Rodríguez García María</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Aquiles Serdán 911</t>
+          <t>5 de Febrero 1887</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Navacoyán</t>
+          <t>Esperanza</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3898,29 +3875,29 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>6183600003</t>
+          <t>6181696059</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VIS-1072</t>
+          <t>VIS-1008</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sánchez García Luis</t>
+          <t>Rodríguez López Carlos</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Coronado 246</t>
+          <t>5 de Febrero 160</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Benito Juárez</t>
+          <t>LOS ANGELES</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3930,29 +3907,29 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>6183312321</t>
+          <t>6182810713</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VIS-1066</t>
+          <t>VIS-1073</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sánchez Hernández Claudia</t>
+          <t>Rodríguez Pérez Rosa</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Aquiles Serdán 1190</t>
+          <t>Juárez 749</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Domingo Arrieta</t>
+          <t>FRACC. VALLE DEL SUR</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3962,29 +3939,29 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>6188588478</t>
+          <t>6184212026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VIS-1012</t>
+          <t>VIS-1109</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sánchez López Jorge</t>
+          <t>Rodríguez Ramírez Francisco</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pino Suárez 695</t>
+          <t>Bruno Martínez 1441</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Villa Montemorelos</t>
+          <t>Ciénega</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3994,29 +3971,29 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>6181430773</t>
+          <t>6185756818</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>VIS-1024</t>
+          <t>VIS-1116</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sánchez Ortiz Carlos</t>
+          <t>Rodríguez Ramírez Juan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pino Suárez 765</t>
+          <t>Zaragoza 844</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Hipódromo</t>
+          <t>Villa Montemorelos</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4026,29 +4003,29 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>6186276714</t>
+          <t>6183345089</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VIS-1051</t>
+          <t>VIS-1097</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sánchez Quiñones Rosa</t>
+          <t>Rodríguez Ramírez Laura</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>5 de Febrero 852</t>
+          <t>20 de Noviembre 1671</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Silvestre Revueltas</t>
+          <t>Cinco de Mayo</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4058,29 +4035,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>6186479731</t>
+          <t>6184045895</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VIS-1098</t>
+          <t>VIS-1062</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sánchez Reyes María</t>
+          <t>Rodríguez Ramírez Luis</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Aquiles Serdán 1453</t>
+          <t>5 de Febrero 1098</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Jardines de Durango</t>
+          <t>Col. Jardines de Durango</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4090,29 +4067,29 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>6187422394</t>
+          <t>6184662374</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VIS-1058</t>
+          <t>VIS-1043</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sánchez Rodríguez Guadalupe</t>
+          <t>Rodríguez Reyes Rosa</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Negrete 165</t>
+          <t>Bruno Martínez 1926</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Fracc. Fidel Velázquez II</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4122,29 +4099,29 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>6182374790</t>
+          <t>6186485488</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>VIS-1005</t>
+          <t>VIS-1144</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sánchez Rodríguez Rosa</t>
+          <t>Rodríguez Rodríguez Ana</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bruno Martínez 673</t>
+          <t>Pino Suárez 1111</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Nueva Vizcaya</t>
+          <t>Morcillo</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4154,29 +4131,29 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>6186037287</t>
+          <t>6182215819</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VIS-1002</t>
+          <t>VIS-1035</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sánchez Soto Carlos</t>
+          <t>Rodríguez Rodríguez José</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Felipe Pescador 453</t>
+          <t>Bruno Martínez 1944</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Fracc. Valle del Sur</t>
+          <t>LOS ANGELES</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4186,29 +4163,29 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>6185390925</t>
+          <t>6187998668</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VIS-1021</t>
+          <t>VIS-1118</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sánchez Valles Verónica</t>
+          <t>Rodríguez Soto Carlos</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bruno Martínez 175</t>
+          <t>Pino Suárez 694</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Silvestre Revueltas</t>
+          <t>Fidel Velázquez</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4218,29 +4195,29 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>6188066915</t>
+          <t>6184999873</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>VIS-1052</t>
+          <t>VIS-1112</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Valles Castro Miguel</t>
+          <t>Rodríguez Soto Luis</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 741</t>
+          <t>Hidalgo 1291</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Lucio Cabañas</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4250,29 +4227,29 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>6188353296</t>
+          <t>6182233197</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VIS-1115</t>
+          <t>VIS-1147</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Valles Rodríguez Claudia</t>
+          <t>Rodríguez Soto María</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coronado 1288</t>
+          <t>Zaragoza 963</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Jardines de Durango</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4282,39 +4259,999 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>6184252783</t>
+          <t>6183452651</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>VIS-1022</t>
+          <t>VIS-1077</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Valles Sánchez Verónica</t>
+          <t>Soto Flores José</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cuauhtémoc 541</t>
+          <t>Juárez 1376</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>José Revueltas</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>6184317339</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>VIS-1145</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Soto Flores María</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Constitución 1650</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Gobernadores</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>6181064898</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>VIS-1083</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Soto García Francisco</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Constitución 298</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Cinco de Mayo</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>6188073787</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>VIS-1061</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Soto Hernández Ana</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Juárez 269</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Fracc. Huizache 2</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>6188397094</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>VIS-1055</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Soto Hernández Juan</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Negrete 657</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Gobernadores</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>6189731248</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>VIS-1023</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Soto López Juan</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Juárez 502</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>El Pueblito</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>6189095278</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>VIS-1143</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Soto López Rosa</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Juárez 792</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Navacoyán</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>6187616641</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>VIS-1126</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Soto Martínez José</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Zaragoza 1016</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Colonia Inventada XYZ</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>6184576309</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>VIS-1015</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Soto Martínez Luis</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Constitución 338</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Ejido Contreras</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>6188059107</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>VIS-1066</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Soto Ramírez Jorge</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Pino Suárez 1170</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>El Arenal</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>6185303580</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>VIS-1086</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Soto Ramírez Jorge</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>20 de Noviembre 1129</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Las Alamedas II</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>6182183668</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>VIS-1078</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Soto Ramírez Luis</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Hidalgo 869</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Dolores Hidalgo</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>6189880980</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>VIS-1081</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Soto Reyes Ana</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Pino Suárez 746</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>6186284628</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>VIS-1076</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Soto Rodríguez Guadalupe</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Victoria 1121</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>FRACC. VALLE DEL SUR</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>6189383179</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>VIS-1134</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Soto Sánchez Patricia</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Victoria 1981</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Ciénega</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>6188348298</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>VIS-1041</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Sánchez Flores Jorge</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Bruno Martínez 623</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Zona Centro</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>6187173199</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>VIS-1119</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sánchez García Carlos</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>5 de Febrero 1706</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>El Arenal</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>6187026105</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>VIS-1033</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Sánchez García Laura</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>5 de Febrero 753</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Fidel Velázquez</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>6182215208</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>VIS-1071</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sánchez García Laura</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Pino Suárez 234</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Guillermina</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>6188699649</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>VIS-1087</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Sánchez García María</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Hidalgo 1660</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Colonia José Ángel Leal</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>6189637318</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>VIS-1099</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Sánchez García María</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>20 de Noviembre 1408</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Colonia Inventada XYZ</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>6181831643</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>VIS-1002</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Sánchez González Juan</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Zaragoza 1203</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Fracc. Huizache 2</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>6187646461</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>VIS-1054</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Sánchez González Juan</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Hidalgo 1646</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
           <t>Labor de Guadalupe</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Durango</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>6184149252</t>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>6189973269</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>VIS-1064</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Sánchez Martínez Carlos</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Juárez 1820</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Villa Montemorelos</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>6189264142</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>VIS-1127</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Sánchez Pérez Laura</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>5 de Febrero 898</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>El Ciprés</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>6187189953</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>VIS-1000</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Sánchez Ramírez Rosa</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Bruno Martínez 1140</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Amp. PRI</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>6184186027</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>VIS-1003</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Sánchez Reyes Laura</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Victoria 1431</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Real del Prado</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>6181251670</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>VIS-1059</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Sánchez Rodríguez Jorge</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Negrete 302</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Huizache I</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>6184578522</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>VIS-1005</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Sánchez Rodríguez Rosa</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Victoria 1825</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Las Alamedas II</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>6189709457</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>VIS-1125</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Sánchez Sánchez Ana</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Negrete 792</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Tierra y Libertad</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>6189294752</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>VIS-1039</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Sánchez Sánchez Carlos</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Zaragoza 1162</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>El Arenal</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>6181499790</t>
         </is>
       </c>
     </row>
